--- a/data/dividends_info_20260310.xlsx
+++ b/data/dividends_info_20260310.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>50.70000076293945</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="I2" t="n">
-        <v>1.380670590663352</v>
+        <v>1.355275855411678</v>
       </c>
       <c r="J2" t="n">
         <v>349</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>21.46999931335449</v>
+        <v>21.8700008392334</v>
       </c>
       <c r="I3" t="n">
-        <v>3.959012702302668</v>
+        <v>3.886602502891329</v>
       </c>
       <c r="J3" t="n">
         <v>104</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6.455999851226807</v>
+        <v>6.458000183105469</v>
       </c>
       <c r="I4" t="n">
-        <v>2.808240461243944</v>
+        <v>2.807370623405867</v>
       </c>
       <c r="J4" t="n">
         <v>104</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>10.4350004196167</v>
+        <v>10.77000045776367</v>
       </c>
       <c r="I5" t="n">
-        <v>2.779108656812611</v>
+        <v>2.692664695208534</v>
       </c>
       <c r="J5" t="n">
         <v>69</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>32.40000152587891</v>
+        <v>33.95999908447266</v>
       </c>
       <c r="I6" t="n">
-        <v>6.172839215462804</v>
+        <v>5.889281666425159</v>
       </c>
       <c r="J6" t="n">
         <v>69</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.875999927520752</v>
+        <v>4.070000171661377</v>
       </c>
       <c r="I7" t="n">
-        <v>2.579979408409435</v>
+        <v>2.457002353372873</v>
       </c>
       <c r="J7" t="n">
         <v>69</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>72.18000030517578</v>
+        <v>73.73999786376953</v>
       </c>
       <c r="I8" t="n">
-        <v>1.440842332506093</v>
+        <v>1.410360767736041</v>
       </c>
       <c r="J8" t="n">
         <v>69</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>50.70000076293945</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="I9" t="n">
-        <v>4.339250427799106</v>
+        <v>4.259438402722417</v>
       </c>
       <c r="J9" t="n">
         <v>69</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>19.21500015258789</v>
+        <v>19.55500030517578</v>
       </c>
       <c r="I10" t="n">
-        <v>4.111371291837342</v>
+        <v>4.03988743375731</v>
       </c>
       <c r="J10" t="n">
         <v>69</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5.204999923706055</v>
+        <v>5.36299991607666</v>
       </c>
       <c r="I11" t="n">
-        <v>3.65033626868368</v>
+        <v>3.542793268193743</v>
       </c>
       <c r="J11" t="n">
         <v>69</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10.35000038146973</v>
+        <v>10.36999988555908</v>
       </c>
       <c r="I12" t="n">
-        <v>4.173912889640444</v>
+        <v>4.165863112511591</v>
       </c>
       <c r="J12" t="n">
         <v>69</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24.6200008392334</v>
+        <v>24.34000015258789</v>
       </c>
       <c r="I13" t="n">
-        <v>1.787164845660096</v>
+        <v>1.807723899924537</v>
       </c>
       <c r="J13" t="n">
         <v>69</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>54.27999877929688</v>
+        <v>55.29999923706055</v>
       </c>
       <c r="I14" t="n">
-        <v>2.579218923147763</v>
+        <v>2.531645604547781</v>
       </c>
       <c r="J14" t="n">
         <v>69</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.871000051498413</v>
+        <v>2.944000005722046</v>
       </c>
       <c r="I15" t="n">
-        <v>10.44932060671423</v>
+        <v>10.19021737149834</v>
       </c>
       <c r="J15" t="n">
         <v>69</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>22.76000022888184</v>
+        <v>23.19000053405762</v>
       </c>
       <c r="I16" t="n">
-        <v>2.636203839921829</v>
+        <v>2.587322062019014</v>
       </c>
       <c r="J16" t="n">
         <v>69</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8.260000228881836</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I17" t="n">
-        <v>6.180387237944506</v>
+        <v>5.93604624832303</v>
       </c>
       <c r="J17" t="n">
         <v>55</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18.29999923706055</v>
+        <v>18.5</v>
       </c>
       <c r="I18" t="n">
-        <v>4.098360826601157</v>
+        <v>4.054054054054054</v>
       </c>
       <c r="J18" t="n">
         <v>55</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3.769999980926514</v>
+        <v>3.934999942779541</v>
       </c>
       <c r="I19" t="n">
-        <v>3.978779860978569</v>
+        <v>3.811944146917711</v>
       </c>
       <c r="J19" t="n">
         <v>55</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>11.76000022888184</v>
+        <v>11.96000003814697</v>
       </c>
       <c r="I20" t="n">
-        <v>1.676607110225773</v>
+        <v>1.648570228855522</v>
       </c>
       <c r="J20" t="n">
         <v>55</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>25.25</v>
+        <v>25.85000038146973</v>
       </c>
       <c r="I21" t="n">
-        <v>4.356435643564357</v>
+        <v>4.255319086140217</v>
       </c>
       <c r="J21" t="n">
         <v>55</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10.19999980926514</v>
+        <v>10.25</v>
       </c>
       <c r="I22" t="n">
-        <v>3.725490265743223</v>
+        <v>3.707317073170731</v>
       </c>
       <c r="J22" t="n">
         <v>55</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.194999933242798</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I23" t="n">
-        <v>2.961275716485869</v>
+        <v>2.863436147407802</v>
       </c>
       <c r="J23" t="n">
         <v>48</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6.53000020980835</v>
+        <v>6.695000171661377</v>
       </c>
       <c r="I24" t="n">
-        <v>7.656967594717345</v>
+        <v>7.468259703956423</v>
       </c>
       <c r="J24" t="n">
         <v>41</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>11.35999965667725</v>
+        <v>11.71500015258789</v>
       </c>
       <c r="I25" t="n">
-        <v>4.753521270421833</v>
+        <v>4.609474971971826</v>
       </c>
       <c r="J25" t="n">
         <v>41</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6.334000110626221</v>
+        <v>6.407999992370605</v>
       </c>
       <c r="I26" t="n">
-        <v>1.578781153354185</v>
+        <v>1.560549315216299</v>
       </c>
       <c r="J26" t="n">
         <v>41</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>295</v>
+        <v>300.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.225423728813559</v>
+        <v>1.202995008319468</v>
       </c>
       <c r="J27" t="n">
         <v>41</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>25.89999961853027</v>
+        <v>26</v>
       </c>
       <c r="I28" t="n">
-        <v>5.250965328304414</v>
+        <v>5.230769230769231</v>
       </c>
       <c r="J28" t="n">
         <v>41</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.40999984741211</v>
+        <v>13.84000015258789</v>
       </c>
       <c r="I29" t="n">
-        <v>4.36241615702102</v>
+        <v>4.226878566114849</v>
       </c>
       <c r="J29" t="n">
         <v>41</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>15.38500022888184</v>
+        <v>16.15999984741211</v>
       </c>
       <c r="I30" t="n">
-        <v>4.094897566639736</v>
+        <v>3.898514888296174</v>
       </c>
       <c r="J30" t="n">
         <v>41</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>97.01999664306641</v>
+        <v>101.8000030517578</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9276438168835157</v>
+        <v>0.8840864175047385</v>
       </c>
       <c r="J31" t="n">
         <v>41</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>65.08999633789062</v>
+        <v>68.80999755859375</v>
       </c>
       <c r="I32" t="n">
-        <v>2.643724223100434</v>
+        <v>2.500799391156333</v>
       </c>
       <c r="J32" t="n">
         <v>41</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>23.70000076293945</v>
+        <v>24.60000038146973</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5907172805619613</v>
+        <v>0.5691056822318461</v>
       </c>
       <c r="J33" t="n">
         <v>34</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1.570000052452087</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I34" t="n">
-        <v>3.821655923277815</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J34" t="n">
         <v>34</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>20.9950008392334</v>
+        <v>20.8700008392334</v>
       </c>
       <c r="I35" t="n">
-        <v>1.238390043377076</v>
+        <v>1.245807328915998</v>
       </c>
       <c r="J35" t="n">
         <v>13</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>27.68000030517578</v>
+        <v>29.21999931335449</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3251445050857577</v>
+        <v>0.3080082207902964</v>
       </c>
       <c r="J36" t="n">
         <v>13</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>50.70000076293945</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="I37" t="n">
-        <v>1.282051262758827</v>
+        <v>1.258470437167987</v>
       </c>
       <c r="J37" t="n">
         <v>-15</v>
@@ -2238,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C375"/>
+  <dimension ref="A1:C275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,14 +2424,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2475,14 +2475,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2492,14 +2492,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2516,29 +2516,29 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2550,46 +2550,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2618,12 +2618,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2640,24 +2640,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2669,12 +2669,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2696,14 +2696,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2713,14 +2713,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2737,7 +2737,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2747,14 +2747,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2788,7 +2788,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2805,7 +2805,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2815,14 +2815,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2832,14 +2832,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2856,7 +2856,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2866,14 +2866,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2883,14 +2883,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2907,7 +2907,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2917,14 +2917,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2941,7 +2941,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2958,7 +2958,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2992,7 +2992,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3002,14 +3002,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3026,7 +3026,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3036,14 +3036,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3053,14 +3053,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3077,7 +3077,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3087,14 +3087,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3104,14 +3104,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3128,12 +3128,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3145,12 +3145,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3162,29 +3162,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3196,12 +3196,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3213,12 +3213,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3230,12 +3230,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3247,46 +3247,46 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3298,7 +3298,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3315,7 +3315,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3349,7 +3349,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3366,29 +3366,29 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3400,80 +3400,80 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3485,29 +3485,29 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3519,12 +3519,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3536,80 +3536,80 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3621,12 +3621,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3638,46 +3638,46 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3689,29 +3689,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3723,29 +3723,29 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3757,12 +3757,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3774,12 +3774,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3808,12 +3808,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3825,63 +3825,63 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3893,29 +3893,29 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3927,12 +3927,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3944,63 +3944,63 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4012,12 +4012,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4029,12 +4029,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -4046,12 +4046,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4063,29 +4063,29 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4097,46 +4097,46 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4148,29 +4148,29 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4182,46 +4182,46 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4233,46 +4233,46 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4284,12 +4284,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4301,12 +4301,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4318,12 +4318,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4335,29 +4335,29 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4369,12 +4369,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4386,12 +4386,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -4403,63 +4403,63 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4471,29 +4471,29 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4505,46 +4505,46 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4556,12 +4556,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4573,29 +4573,29 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4607,63 +4607,63 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4675,12 +4675,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4692,46 +4692,46 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4743,29 +4743,29 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4777,12 +4777,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4794,12 +4794,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4811,12 +4811,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4828,12 +4828,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4845,12 +4845,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4862,12 +4862,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4879,12 +4879,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4896,29 +4896,29 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4930,29 +4930,29 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4964,12 +4964,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4981,29 +4981,29 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5015,12 +5015,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5032,29 +5032,29 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -5066,12 +5066,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5083,12 +5083,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -5100,12 +5100,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5117,12 +5117,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5134,12 +5134,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5151,12 +5151,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5168,12 +5168,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5185,12 +5185,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5202,63 +5202,63 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5270,63 +5270,63 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5338,12 +5338,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5355,29 +5355,29 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5389,12 +5389,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5406,12 +5406,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5423,12 +5423,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5440,12 +5440,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5457,12 +5457,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5474,12 +5474,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5491,12 +5491,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5508,12 +5508,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5525,12 +5525,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5542,12 +5542,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5559,29 +5559,29 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5593,29 +5593,29 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5627,29 +5627,29 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5661,12 +5661,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5678,12 +5678,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5695,12 +5695,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5712,12 +5712,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5729,29 +5729,29 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5763,12 +5763,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5780,12 +5780,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5797,12 +5797,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5814,12 +5814,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5831,12 +5831,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5848,29 +5848,29 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5882,29 +5882,29 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -5916,12 +5916,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -5933,12 +5933,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -5950,29 +5950,29 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -5984,46 +5984,46 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6035,29 +6035,29 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6069,63 +6069,63 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6137,12 +6137,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6154,12 +6154,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6171,12 +6171,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6188,12 +6188,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6205,29 +6205,29 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6239,12 +6239,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6256,29 +6256,29 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6290,12 +6290,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6307,12 +6307,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6324,12 +6324,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6341,12 +6341,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -6358,12 +6358,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -6375,12 +6375,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -6392,12 +6392,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -6409,12 +6409,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -6426,12 +6426,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -6443,12 +6443,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -6460,46 +6460,46 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -6511,12 +6511,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -6528,12 +6528,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -6545,29 +6545,29 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -6579,12 +6579,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -6596,12 +6596,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -6613,12 +6613,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -6630,12 +6630,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -6647,29 +6647,29 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -6681,12 +6681,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -6698,12 +6698,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -6715,12 +6715,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -6732,80 +6732,80 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -6817,63 +6817,63 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -6885,1734 +6885,34 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>COFLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>HEALTH ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>Gentili Mosconi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>BFF Bank S.P.A.</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Farmacosmo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>FRANCHETTI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>EUKEDOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Ambromobiliare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>ACQUAZZURRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>AATECH S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>Energy S.p.A.</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>Emma Villas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>EdgeLab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>E-Globe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Markbass S.p.A.</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>ILPRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>MIT SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>Tenax International S.p.A.</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>doxee S.p.A.</t>
-        </is>
-      </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>iVision Tech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>MONDO TV FRANCE</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>Pasquarelli Auto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>T.P.S. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>PLANETEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Otofarma S.p.A.</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>PROMOTICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>Annual Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>OLIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Novamarine S.p.A.</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Haiki+ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>INNOVATEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>Litix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>KALEON S.P.A.</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Leone Film Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Vantea Smart S.p.A.</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Valica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Solid World Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>BUZZI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>CALEFFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Vivenda Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Com.Tel S.p.A.</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>WEBSOLUTE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Pozzi Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Dedem S.p.A.</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>MONDO TV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Execus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Ferretti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>GEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Lucisano Media Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Reway Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>ROSETTI MARINO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>OPS ECOM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>NEUROSOFT</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Digital Value S.p.A.</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr">
-        <is>
           <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C375" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -8627,104 +6927,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001018362</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>10.19999980926514</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.725490265743223</v>
-      </c>
-      <c r="I2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8735,129 +6940,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BORGOSESIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Friends S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Gas Plus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>